--- a/01-price-parser/examples/products.xlsx
+++ b/01-price-parser/examples/products.xlsx
@@ -485,8 +485,10 @@
       <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -516,8 +518,10 @@
       <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -547,8 +551,10 @@
       <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -578,8 +584,10 @@
       <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -609,8 +617,10 @@
       <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="b">
-        <v>1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -640,8 +650,10 @@
       <c r="D7" t="n">
         <v>4</v>
       </c>
-      <c r="E7" t="b">
-        <v>1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -671,8 +683,10 @@
       <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -702,8 +716,10 @@
       <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -733,8 +749,10 @@
       <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="b">
-        <v>1</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -764,8 +782,10 @@
       <c r="D11" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="b">
-        <v>1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -795,8 +815,10 @@
       <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="b">
-        <v>1</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -826,8 +848,10 @@
       <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="b">
-        <v>1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -857,8 +881,10 @@
       <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="b">
-        <v>1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -888,8 +914,10 @@
       <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="b">
-        <v>1</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -919,8 +947,10 @@
       <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="b">
-        <v>1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -950,8 +980,10 @@
       <c r="D17" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="b">
-        <v>1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -981,8 +1013,10 @@
       <c r="D18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="b">
-        <v>1</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1012,8 +1046,10 @@
       <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="b">
-        <v>1</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1043,8 +1079,10 @@
       <c r="D20" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="b">
-        <v>1</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1074,8 +1112,10 @@
       <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="b">
-        <v>1</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1105,8 +1145,10 @@
       <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="b">
-        <v>1</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1136,8 +1178,10 @@
       <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="b">
-        <v>1</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1167,8 +1211,10 @@
       <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="b">
-        <v>1</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1198,8 +1244,10 @@
       <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="b">
-        <v>1</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1229,8 +1277,10 @@
       <c r="D26" t="n">
         <v>4</v>
       </c>
-      <c r="E26" t="b">
-        <v>1</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1260,8 +1310,10 @@
       <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="E27" t="b">
-        <v>1</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1291,8 +1343,10 @@
       <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="b">
-        <v>1</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1322,8 +1376,10 @@
       <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="b">
-        <v>1</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1353,8 +1409,10 @@
       <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="b">
-        <v>1</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1384,8 +1442,10 @@
       <c r="D31" t="n">
         <v>4</v>
       </c>
-      <c r="E31" t="b">
-        <v>1</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1415,8 +1475,10 @@
       <c r="D32" t="n">
         <v>4</v>
       </c>
-      <c r="E32" t="b">
-        <v>1</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1446,8 +1508,10 @@
       <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="E33" t="b">
-        <v>1</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1477,8 +1541,10 @@
       <c r="D34" t="n">
         <v>3</v>
       </c>
-      <c r="E34" t="b">
-        <v>1</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1508,8 +1574,10 @@
       <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="E35" t="b">
-        <v>1</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1539,8 +1607,10 @@
       <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E36" t="b">
-        <v>1</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1570,8 +1640,10 @@
       <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="E37" t="b">
-        <v>1</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1601,8 +1673,10 @@
       <c r="D38" t="n">
         <v>3</v>
       </c>
-      <c r="E38" t="b">
-        <v>1</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/01-price-parser/examples/products.xlsx
+++ b/01-price-parser/examples/products.xlsx
@@ -7,10 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Изменения цен" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Новые товары" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Товары'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Изменения цен'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,14 +35,41 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE2E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F5E6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,15 +81,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,50 +465,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Отчёт о ценах</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Books to Scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Дата запуска</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24.10.2026 14:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Страниц обработано</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Товаров собрано</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Товаров в выгрузке (после фильтров)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Подорожало</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Подешевело</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Новых товаров</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Пропало из каталога</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Валюта</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Рейтинг</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Картинка</t>
         </is>
@@ -474,7 +632,7 @@
           <t>A Light in the Attic</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>51.77</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -490,7 +648,7 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>https://books.toscrape.com/catalogue/a-light-in-the-attic_1000/index.html</t>
         </is>
@@ -507,7 +665,7 @@
           <t>Sharp Objects</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>47.82</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -523,7 +681,7 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>https://books.toscrape.com/catalogue/sharp-objects_997/index.html</t>
         </is>
@@ -540,7 +698,7 @@
           <t>Sapiens: A Brief History of Humankind</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>54.23</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,7 +714,7 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>https://books.toscrape.com/catalogue/sapiens-a-brief-history-of-humankind_996/index.html</t>
         </is>
@@ -573,7 +731,7 @@
           <t>The Dirty Little Secrets of Getting Your Dream Job</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>33.34</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -589,7 +747,7 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>https://books.toscrape.com/catalogue/the-dirty-little-secrets-of-getting-your-dream-job_994/index.html</t>
         </is>
@@ -606,7 +764,7 @@
           <t>The Coming Woman: A Novel Based on the Life of the Infamous Feminist, Victoria Woodhull</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>17.93</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,7 +780,7 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>https://books.toscrape.com/catalogue/the-coming-woman-a-novel-based-on-the-life-of-the-infamous-feminist-victoria-woodhull_993/index.html</t>
         </is>
@@ -639,7 +797,7 @@
           <t>The Boys in the Boat: Nine Americans and Their Epic Quest for Gold at the 1936 Berlin Olympics</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -655,7 +813,7 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>https://books.toscrape.com/catalogue/the-boys-in-the-boat-nine-americans-and-their-epic-quest-for-gold-at-the-1936-berlin-olympics_992/index.html</t>
         </is>
@@ -669,11 +827,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shakespeare's Sonnets</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>20.66</v>
+          <t>Starving Hearts (Triangular Trade Trilogy, #1)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>13.99</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -681,32 +839,32 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/shakespeares-sonnets_989/index.html</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/starving-hearts-triangular-trade-trilogy-1_990/index.html</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/10/48/1048f63d3b5061cd2f424d20b3f9b666.jpg</t>
+          <t>https://books.toscrape.com/media/cache/be/f4/bef44da28c98f905a3ebec0b87be8530.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Set Me Free</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>17.46</v>
+          <t>Shakespeare's Sonnets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>20.66</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -714,32 +872,32 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/set-me-free_988/index.html</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/shakespeares-sonnets_989/index.html</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/5b/88/5b88c52633f53cacf162c15f4f823153.jpg</t>
+          <t>https://books.toscrape.com/media/cache/10/48/1048f63d3b5061cd2f424d20b3f9b666.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scott Pilgrim's Precious Little Life (Scott Pilgrim #1)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>52.29</v>
+          <t>Set Me Free</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>17.46</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -754,25 +912,25 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/scott-pilgrims-precious-little-life-scott-pilgrim-1_987/index.html</t>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/set-me-free_988/index.html</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/94/b1/94b1b8b244bce9677c2f29ccc890d4d2.jpg</t>
+          <t>https://books.toscrape.com/media/cache/5b/88/5b88c52633f53cacf162c15f4f823153.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rip it Up and Start Again</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>35.02</v>
+          <t>Scott Pilgrim's Precious Little Life (Scott Pilgrim #1)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>52.29</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -787,25 +945,25 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/rip-it-up-and-start-again_986/index.html</t>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/scott-pilgrims-precious-little-life-scott-pilgrim-1_987/index.html</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/81/c4/81c4a973364e17d01f217e1188253d5e.jpg</t>
+          <t>https://books.toscrape.com/media/cache/94/b1/94b1b8b244bce9677c2f29ccc890d4d2.jpg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Our Band Could Be Your Life: Scenes from the American Indie Underground, 1981-1991</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>57.25</v>
+          <t>Rip it Up and Start Again</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>35.02</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -813,32 +971,32 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/our-band-could-be-your-life-scenes-from-the-american-indie-underground-1981-1991_985/index.html</t>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/rip-it-up-and-start-again_986/index.html</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/54/60/54607fe8945897cdcced0044103b10b6.jpg</t>
+          <t>https://books.toscrape.com/media/cache/81/c4/81c4a973364e17d01f217e1188253d5e.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Foolproof Preserving: A Guide to Small Batch Jams, Jellies, Pickles, Condiments, and More: A Foolproof Guide to Making Small Batch Jams, Jellies, Pickles, Condiments, and More</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>30.52</v>
+          <t>Our Band Could Be Your Life: Scenes from the American Indie Underground, 1981-1991</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>57.25</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -853,25 +1011,25 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/foolproof-preserving-a-guide-to-small-batch-jams-jellies-pickles-condiments-and-more-a-foolproof-guide-to-making-small-batch-jams-jellies-pickles-condiments-and-more_978/index.html</t>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/our-band-could-be-your-life-scenes-from-the-american-indie-underground-1981-1991_985/index.html</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/9f/59/9f59f01fa916a7bb8f0b28a4012179a4.jpg</t>
+          <t>https://books.toscrape.com/media/cache/54/60/54607fe8945897cdcced0044103b10b6.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chase Me (Paris Nights #2)</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>25.27</v>
+          <t>Libertarianism for Beginners</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>51.33</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -879,32 +1037,32 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/chase-me-paris-nights-2_977/index.html</t>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/libertarianism-for-beginners_982/index.html</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/9c/2e/9c2e0eb8866b8e3f3b768994fd3d1c1a.jpg</t>
+          <t>https://books.toscrape.com/media/cache/0b/bc/0bbcd0a6f4bcd81ccb1049a52736406e.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Black Dust</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>34.53</v>
+          <t>It's Only the Himalayas</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>45.17</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -912,32 +1070,32 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/black-dust_976/index.html</t>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/its-only-the-himalayas_981/index.html</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/44/cc/44ccc99c8f82c33d4f9d2afa4ef25787.jpg</t>
+          <t>https://books.toscrape.com/media/cache/27/a5/27a53d0bb95bdd88288eaf66c9230d7e.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Birdsong: A Story in Pictures</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>54.64</v>
+          <t>How Music Works</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>37.32</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -945,32 +1103,32 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/birdsong-a-story-in-pictures_975/index.html</t>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/how-music-works_979/index.html</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/af/6e/af6e796160fe63e0cf19d44395c7ddf2.jpg</t>
+          <t>https://books.toscrape.com/media/cache/5c/c8/5cc8e107246cb478960d4f0aba1e1c8e.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>America's Cradle of Quarterbacks: Western Pennsylvania's Football Factory from Johnny Unitas to Joe Montana</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>22.5</v>
+          <t>Foolproof Preserving: A Guide to Small Batch Jams, Jellies, Pickles, Condiments, and More: A Foolproof Guide to Making Small Batch Jams, Jellies, Pickles, Condiments, and More</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>30.52</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -985,25 +1143,25 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/americas-cradle-of-quarterbacks-western-pennsylvanias-football-factory-from-johnny-unitas-to-joe-montana_974/index.html</t>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/foolproof-preserving-a-guide-to-small-batch-jams-jellies-pickles-condiments-and-more-a-foolproof-guide-to-making-small-batch-jams-jellies-pickles-condiments-and-more_978/index.html</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/ef/0b/ef0bed08de4e083dba5e20fdb98d9c36.jpg</t>
+          <t>https://books.toscrape.com/media/cache/9f/59/9f59f01fa916a7bb8f0b28a4012179a4.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aladdin and His Wonderful Lamp</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>53.13</v>
+          <t>Chase Me (Paris Nights #2)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>25.27</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1011,32 +1169,32 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/aladdin-and-his-wonderful-lamp_973/index.html</t>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/chase-me-paris-nights-2_977/index.html</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/d6/da/d6da0371958068bbaf39ea9c174275cd.jpg</t>
+          <t>https://books.toscrape.com/media/cache/9c/2e/9c2e0eb8866b8e3f3b768994fd3d1c1a.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Worlds Elsewhere: Journeys Around Shakespeare’s Globe</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>40.3</v>
+          <t>Black Dust</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>34.53</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1051,25 +1209,25 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/worlds-elsewhere-journeys-around-shakespeares-globe_972/index.html</t>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/black-dust_976/index.html</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/2e/98/2e98c332bf8563b584784971541c4445.jpg</t>
+          <t>https://books.toscrape.com/media/cache/44/cc/44ccc99c8f82c33d4f9d2afa4ef25787.jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wall and Piece</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>44.18</v>
+          <t>Birdsong: A Story in Pictures</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>54.64</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1077,32 +1235,32 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/wall-and-piece_971/index.html</t>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/birdsong-a-story-in-pictures_975/index.html</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/a5/41/a5416b9646aaa7287baa287ec2590270.jpg</t>
+          <t>https://books.toscrape.com/media/cache/af/6e/af6e796160fe63e0cf19d44395c7ddf2.jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>17.66</v>
+          <t>America's Cradle of Quarterbacks: Western Pennsylvania's Football Factory from Johnny Unitas to Joe Montana</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1110,32 +1268,32 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/the-four-agreements-a-practical-guide-to-personal-freedom_970/index.html</t>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/americas-cradle-of-quarterbacks-western-pennsylvanias-football-factory-from-johnny-unitas-to-joe-montana_974/index.html</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/0f/7e/0f7ee69495c0df1d35723f012624a9f8.jpg</t>
+          <t>https://books.toscrape.com/media/cache/ef/0b/ef0bed08de4e083dba5e20fdb98d9c36.jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>The Five Love Languages: How to Express Heartfelt Commitment to Your Mate</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>31.05</v>
+          <t>Aladdin and His Wonderful Lamp</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>53.13</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1150,25 +1308,25 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/the-five-love-languages-how-to-express-heartfelt-commitment-to-your-mate_969/index.html</t>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/aladdin-and-his-wonderful-lamp_973/index.html</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/38/c5/38c56fba316c07305643a8065269594e.jpg</t>
+          <t>https://books.toscrape.com/media/cache/d6/da/d6da0371958068bbaf39ea9c174275cd.jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>The Elephant Tree</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>23.82</v>
+          <t>Worlds Elsewhere: Journeys Around Shakespeare’s Globe</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>40.3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1183,25 +1341,25 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/the-elephant-tree_968/index.html</t>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/worlds-elsewhere-journeys-around-shakespeares-globe_972/index.html</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/5d/7e/5d7ecde8e81513eba8a64c9fe000744b.jpg</t>
+          <t>https://books.toscrape.com/media/cache/2e/98/2e98c332bf8563b584784971541c4445.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sophie's World</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>15.94</v>
+          <t>Wall and Piece</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>44.18</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1209,32 +1367,32 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/sophies-world_966/index.html</t>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/wall-and-piece_971/index.html</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/65/71/6571919836ec51ed54f0050c31d8a0cd.jpg</t>
+          <t>https://books.toscrape.com/media/cache/a5/41/a5416b9646aaa7287baa287ec2590270.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Penny Maybe</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>33.29</v>
+          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>17.66</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1242,32 +1400,32 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/penny-maybe_965/index.html</t>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-four-agreements-a-practical-guide-to-personal-freedom_970/index.html</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/12/53/1253c21c5ef3c6d075c5fa3f5fecee6a.jpg</t>
+          <t>https://books.toscrape.com/media/cache/0f/7e/0f7ee69495c0df1d35723f012624a9f8.jpg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Behind Closed Doors</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>52.22</v>
+          <t>The Five Love Languages: How to Express Heartfelt Commitment to Your Mate</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>31.05</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1275,32 +1433,32 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/behind-closed-doors_962/index.html</t>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-five-love-languages-how-to-express-heartfelt-commitment-to-your-mate_969/index.html</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/e1/5c/e15c289ba58cea38519e1281e859f0c1.jpg</t>
+          <t>https://books.toscrape.com/media/cache/38/c5/38c56fba316c07305643a8065269594e.jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Slow States of Collapse: Poems</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>57.31</v>
+          <t>The Elephant Tree</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>23.82</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1308,32 +1466,32 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/slow-states-of-collapse-poems_960/index.html</t>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-elephant-tree_968/index.html</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/72/41/72417db983862010ef0c1a25de98c7d7.jpg</t>
+          <t>https://books.toscrape.com/media/cache/5d/7e/5d7ecde8e81513eba8a64c9fe000744b.jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Private Paris (Private #10)</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>47.61</v>
+          <t>Sophie's World</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>15.94</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1348,25 +1506,25 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/private-paris-private-10_958/index.html</t>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/sophies-world_966/index.html</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/9d/05/9d0533bae1578846d728a82913b95c26.jpg</t>
+          <t>https://books.toscrape.com/media/cache/65/71/6571919836ec51ed54f0050c31d8a0cd.jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>#HigherSelfie: Wake Up Your Life. Free Your Soul. Find Your Tribe.</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>23.11</v>
+          <t>Penny Maybe</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>33.29</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1374,32 +1532,32 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/higherselfie-wake-up-your-life-free-your-soul-find-your-tribe_957/index.html</t>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/penny-maybe_965/index.html</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/9c/46/9c463c7631c82401160fd3b554b8f0e1.jpg</t>
+          <t>https://books.toscrape.com/media/cache/12/53/1253c21c5ef3c6d075c5fa3f5fecee6a.jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>We Love You, Charlie Freeman</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>50.27</v>
+          <t>Maude (1883-1993):She Grew Up with the country</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>18.02</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1407,32 +1565,32 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/we-love-you-charlie-freeman_954/index.html</t>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/maude-1883-1993she-grew-up-with-the-country_964/index.html</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/5f/15/5f152afdbc42356ecba02f61058a7e5b.jpg</t>
+          <t>https://books.toscrape.com/media/cache/f5/88/f5889d038f5d8e949b494d147c2dcf54.jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Untitled Collection: Sabbath Poems 2014</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>14.27</v>
+          <t>Behind Closed Doors</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>52.22</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1447,250 +1605,403 @@
           <t>да</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/untitled-collection-sabbath-poems-2014_953/index.html</t>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/behind-closed-doors_962/index.html</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://books.toscrape.com/media/cache/f9/3b/f93b4a650f03a5d21f2436d7813f42c2.jpg</t>
+          <t>https://books.toscrape.com/media/cache/e1/5c/e15c289ba58cea38519e1281e859f0c1.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unseen City: The Majesty of Pigeons, the Discreet Charm of Snails &amp; Other Wonders of the Urban Wilderness</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+          <t>You can't bury them all: Poems</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/you-cant-bury-them-all-poems_961/index.html</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/media/cache/e9/20/e9203b733126c4a0832a1c7885dc27cf.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G32"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Разница</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Изменение, %</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>How Music Works</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/how-music-works_979/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Foolproof Preserving: A Guide to Small Batch Jams, Jellies, Pickles, Condiments, and More: A Foolproof Guide to Making Small Batch Jams, Jellies, Pickles, Condiments, and More</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>-7.63</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/foolproof-preserving-a-guide-to-small-batch-jams-jellies-pickles-condiments-and-more-a-foolproof-guide-to-making-small-batch-jams-jellies-pickles-condiments-and-more_978/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Birdsong: A Story in Pictures</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/birdsong-a-story-in-pictures_975/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Behind Closed Doors</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>-7.12</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/behind-closed-doors_962/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Chase Me (Paris Nights #2)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/chase-me-paris-nights-2_977/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Black Dust</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/black-dust_976/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>In a Dark, Dark Wood</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/in-a-dark-dark-wood_963/index.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Worlds Elsewhere: Journeys Around Shakespeare’s Globe</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/worlds-elsewhere-journeys-around-shakespeares-globe_972/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wall and Piece</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>44.18</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/unseen-city-the-majesty-of-pigeons-the-discreet-charm-of-snails-other-wonders-of-the-urban-wilderness_952/index.html</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/media/cache/41/a2/41a20f35adf0caea24f208dc01ad7681.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Unicorn Tracks</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>18.78</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/unicorn-tracks_951/index.html</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/media/cache/76/8e/768ea5924ac1ef6297c2be9959c796c2.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Throwing Rocks at the Google Bus: How Growth Became the Enemy of Prosperity</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/throwing-rocks-at-the-google-bus-how-growth-became-the-enemy-of-prosperity_948/index.html</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/media/cache/03/86/038650c9e7517b4baf2a423cd8eed38f.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>This One Summer</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/this-one-summer_947/index.html</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/media/cache/c4/dd/c4ddd9ced89966b0602ec85e00cd5b61.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Thirst</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>17.27</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/thirst_946/index.html</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/media/cache/c4/0a/c40a64f59e7487b1a80a049f6ceb2ba5.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>The Past Never Ends</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/the-past-never-ends_942/index.html</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/media/cache/89/b8/89b850edb01851a91f64ba114b96acb6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>The Natural History of Us (The Fine Art of Pretending #2)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>45.22</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>£</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/catalogue/the-natural-history-of-us-the-fine-art-of-pretending-2_941/index.html</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://books.toscrape.com/media/cache/5d/7f/5d7f496cdf5e5962a73ecdcc1505c1d5.jpg</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/wall-and-piece_971/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>You can't bury them all: Poems</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/you-cant-bury-them-all-poems_961/index.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>